--- a/SNSPLLua2etc/toEtc/etc.xlsx
+++ b/SNSPLLua2etc/toEtc/etc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>序号</t>
   </si>
@@ -24,6 +24,9 @@
     <t>域名</t>
   </si>
   <si>
+    <t>需求</t>
+  </si>
+  <si>
     <t>边缘下发文件名</t>
   </si>
   <si>
@@ -39,53 +42,31 @@
     <t>1</t>
   </si>
   <si>
-    <t>v6-sc.miguvideo.com</t>
-  </si>
-  <si>
-    <t>/SNS/ats/parent.config
-/SNS/ats/remap.config
-/SNS/nginx/v6-sc.miguvideo.com.conf
+    <t>zqhswlive.itv.cmvideo.cn</t>
+  </si>
+  <si>
+    <t>打开channel-id检查</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/zqhswlive.itv.cmvideo.cn.conf
 </t>
   </si>
   <si>
-    <t>/etc/trafficserver/parent.config
-/etc/trafficserver/remap.config
-/etc/nginx/sites-enabled/v6-sc.miguvideo.com.conf
+    <t>/etc/nginx/sites-enabled/zqhswlive.itv.cmvideo.cn.conf
 </t>
   </si>
   <si>
-    <t>/CCS/ats/remap.config
-/CCS/nginx/v6-sc.miguvideo.com-l2.conf
+    <t>2</t>
+  </si>
+  <si>
+    <t>studentlive.migucloud.com</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/studentlive.migucloud.com.conf
 </t>
   </si>
   <si>
-    <t>/etc/trafficserver/remap.config
-/etc/nginx/sites-enabled/v6-sc.miguvideo.com-l2.conf
-</t>
-  </si>
-  <si>
-    <t>v7-sc.miguvideo.com</t>
-  </si>
-  <si>
-    <t>/SNS/ats/parent.config
-/SNS/ats/remap.config
-/SNS/nginx/v7-sc.miguvideo.com.conf
-</t>
-  </si>
-  <si>
-    <t>/etc/trafficserver/parent.config
-/etc/trafficserver/remap.config
-/etc/nginx/sites-enabled/v7-sc.miguvideo.com.conf
-</t>
-  </si>
-  <si>
-    <t>/CCS/ats/remap.config
-/CCS/nginx/v7-sc.miguvideo.com-l2.conf
-</t>
-  </si>
-  <si>
-    <t>/etc/trafficserver/remap.config
-/etc/nginx/sites-enabled/v7-sc.miguvideo.com-l2.conf
+    <t>/etc/nginx/sites-enabled/studentlive.migucloud.com.conf
 </t>
   </si>
 </sst>
@@ -453,7 +434,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -462,6 +443,7 @@
     <col collapsed="false" hidden="false" max="4" min="4" style="1" width="9.5"/>
     <col collapsed="false" hidden="false" max="5" min="5" style="1" width="9.5"/>
     <col collapsed="false" hidden="false" max="6" min="6" style="1" width="9.5"/>
+    <col collapsed="false" hidden="false" max="7" min="7" style="1" width="9.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,45 +465,42 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/SNSPLLua2etc/toEtc/etc.xlsx
+++ b/SNSPLLua2etc/toEtc/etc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>序号</t>
   </si>
@@ -42,31 +42,52 @@
     <t>1</t>
   </si>
   <si>
-    <t>zqhswlive.itv.cmvideo.cn</t>
-  </si>
-  <si>
-    <t>打开channel-id检查</t>
-  </si>
-  <si>
-    <t>/SNS/nginx/zqhswlive.itv.cmvideo.cn.conf
+    <t>全网log处理lua文件更新</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/lua/originiqiyi/origin_iqiyi_header_filter.lua
+/SNS/nginx/lua/originiqiyi/origin_iqiyi_log.lua
+/SNS/nginx/lua/cdntest.homecloud.komect.com.lua
+/SNS/nginx/lua/tsvp2_migu_logmerge.lua
+/SNS/nginx/lua/toutiao/bytedance_header.lua
+/SNS/nginx/lua/toutiao/bytedance_image_header.lua
+/SNS/nginx/lua/gdyunchen/yunchen_header.lua
+/SNS/nginx/lua/gdyunchen/yunchen_log.lua
+/SNS/nginx/lua/otaup.aiskill.komect.com_log.lua
+/SNS/nginx/lua/gaokao.jilinxiangyun_log.lua
 </t>
   </si>
   <si>
-    <t>/etc/nginx/sites-enabled/zqhswlive.itv.cmvideo.cn.conf
+    <t>/etc/nginx/lua/originiqiyi/origin_iqiyi_header_filter.lua
+/etc/nginx/lua/originiqiyi/origin_iqiyi_log.lua
+/etc/nginx/lua/cdntest.homecloud.komect.com.lua
+/etc/nginx/lua/tsvp2_migu_logmerge.lua
+/etc/nginx/lua/toutiao/bytedance_header.lua
+/etc/nginx/lua/toutiao/bytedance_image_header.lua
+/etc/nginx/lua/gdyunchen/yunchen_header.lua
+/etc/nginx/lua/gdyunchen/yunchen_log.lua
+/etc/nginx/lua/otaup.aiskill.komect.com_log.lua
+/etc/nginx/lua/gaokao.jilinxiangyun_log.lua
 </t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>studentlive.migucloud.com</t>
-  </si>
-  <si>
-    <t>/SNS/nginx/studentlive.migucloud.com.conf
+    <t>/CCS/nginx/lua/originiqiyi/origin_iqiyi_header_filter_l2.lua
+/CCS/nginx/lua/cdntest.homecloud.komect.com.lua
+/CCS/nginx/lua/toutiao/bytedance_zx_scyd_header.lua
+/CCS/nginx/lua/gdyunchen/yunchen_log-l2.lua
+/CCS/nginx/lua/gdyunchen/yunchen_header-l2.lua
+/CCS/nginx/lua/tsvp2_migu_logmerge-l2.lua
+/CCS/nginx/lua/bytedance_zx_header.lua
 </t>
   </si>
   <si>
-    <t>/etc/nginx/sites-enabled/studentlive.migucloud.com.conf
+    <t>/etc/nginx/lua/originiqiyi/origin_iqiyi_header_filter_l2.lua
+/etc/nginx/lua/cdntest.homecloud.komect.com.lua
+/etc/nginx/lua/toutiao/bytedance_zx_scyd_header.lua
+/etc/nginx/lua/gdyunchen/yunchen_log-l2.lua
+/etc/nginx/lua/gdyunchen/yunchen_header-l2.lua
+/etc/nginx/lua/tsvp2_migu_logmerge-l2.lua
+/etc/nginx/lua/bytedance_zx_header.lua
 </t>
   </si>
 </sst>
@@ -434,7 +455,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -477,30 +498,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/SNSPLLua2etc/toEtc/etc.xlsx
+++ b/SNSPLLua2etc/toEtc/etc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>序号</t>
   </si>
@@ -42,52 +42,39 @@
     <t>1</t>
   </si>
   <si>
-    <t>全网log处理lua文件更新</t>
-  </si>
-  <si>
-    <t>/SNS/nginx/lua/originiqiyi/origin_iqiyi_header_filter.lua
-/SNS/nginx/lua/originiqiyi/origin_iqiyi_log.lua
-/SNS/nginx/lua/cdntest.homecloud.komect.com.lua
-/SNS/nginx/lua/tsvp2_migu_logmerge.lua
-/SNS/nginx/lua/toutiao/bytedance_header.lua
-/SNS/nginx/lua/toutiao/bytedance_image_header.lua
-/SNS/nginx/lua/gdyunchen/yunchen_header.lua
-/SNS/nginx/lua/gdyunchen/yunchen_log.lua
-/SNS/nginx/lua/otaup.aiskill.komect.com_log.lua
-/SNS/nginx/lua/gaokao.jilinxiangyun_log.lua
+    <t>ops.zhibang.com</t>
+  </si>
+  <si>
+    <t>全站加速7层新增域名</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/ssl/zhibang.com.key
+/SNS/nginx/ssl/zhibang.com.crt
+/SNS/nginx/ops.zhibang.com.conf
 </t>
   </si>
   <si>
-    <t>/etc/nginx/lua/originiqiyi/origin_iqiyi_header_filter.lua
-/etc/nginx/lua/originiqiyi/origin_iqiyi_log.lua
-/etc/nginx/lua/cdntest.homecloud.komect.com.lua
-/etc/nginx/lua/tsvp2_migu_logmerge.lua
-/etc/nginx/lua/toutiao/bytedance_header.lua
-/etc/nginx/lua/toutiao/bytedance_image_header.lua
-/etc/nginx/lua/gdyunchen/yunchen_header.lua
-/etc/nginx/lua/gdyunchen/yunchen_log.lua
-/etc/nginx/lua/otaup.aiskill.komect.com_log.lua
-/etc/nginx/lua/gaokao.jilinxiangyun_log.lua
+    <t>/etc/nginx/ssl/zhibang.com.key
+/etc/nginx/ssl/zhibang.com.crt
+/etc/nginx/sites-enabled/ops.zhibang.com.conf
 </t>
   </si>
   <si>
-    <t>/CCS/nginx/lua/originiqiyi/origin_iqiyi_header_filter_l2.lua
-/CCS/nginx/lua/cdntest.homecloud.komect.com.lua
-/CCS/nginx/lua/toutiao/bytedance_zx_scyd_header.lua
-/CCS/nginx/lua/gdyunchen/yunchen_log-l2.lua
-/CCS/nginx/lua/gdyunchen/yunchen_header-l2.lua
-/CCS/nginx/lua/tsvp2_migu_logmerge-l2.lua
-/CCS/nginx/lua/bytedance_zx_header.lua
+    <t>2</t>
+  </si>
+  <si>
+    <t>sso.zbom.com</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/ssl/zbom.com.crt
+/SNS/nginx/ssl/zbom.com.key
+/SNS/nginx/sso.zbom.com.conf
 </t>
   </si>
   <si>
-    <t>/etc/nginx/lua/originiqiyi/origin_iqiyi_header_filter_l2.lua
-/etc/nginx/lua/cdntest.homecloud.komect.com.lua
-/etc/nginx/lua/toutiao/bytedance_zx_scyd_header.lua
-/etc/nginx/lua/gdyunchen/yunchen_log-l2.lua
-/etc/nginx/lua/gdyunchen/yunchen_header-l2.lua
-/etc/nginx/lua/tsvp2_migu_logmerge-l2.lua
-/etc/nginx/lua/bytedance_zx_header.lua
+    <t>/etc/nginx/ssl/zbom.com.crt
+/etc/nginx/ssl/zbom.com.key
+/etc/nginx/sites-enabled/sso.zbom.com.conf
 </t>
   </si>
 </sst>
@@ -455,7 +442,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -498,19 +485,30 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/SNSPLLua2etc/toEtc/etc.xlsx
+++ b/SNSPLLua2etc/toEtc/etc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>序号</t>
   </si>
@@ -42,39 +42,137 @@
     <t>1</t>
   </si>
   <si>
-    <t>ops.zhibang.com</t>
-  </si>
-  <si>
-    <t>全站加速7层新增域名</t>
-  </si>
-  <si>
-    <t>/SNS/nginx/ssl/zhibang.com.key
-/SNS/nginx/ssl/zhibang.com.crt
-/SNS/nginx/ops.zhibang.com.conf
-</t>
-  </si>
-  <si>
-    <t>/etc/nginx/ssl/zhibang.com.key
-/etc/nginx/ssl/zhibang.com.crt
-/etc/nginx/sites-enabled/ops.zhibang.com.conf
+    <t>bytedance</t>
+  </si>
+  <si>
+    <t>1、日志||（双竖线）转义异常修复,涉及多个日志lua，2、当range为空时，取值会缺少字段。3、range里带|做转义</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/lua/toutiao/bytedance_header.lua
+/SNS/nginx/lua/toutiao/bytedance_log.lua
+/SNS/nginx/lua/toutiao/bytedance_image_header.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/toutiao/bytedance_header.lua
+/etc/nginx/lua/toutiao/bytedance_log.lua
+/etc/nginx/lua/toutiao/bytedance_image_header.lua
+</t>
+  </si>
+  <si>
+    <t>/CCS/nginx/lua/toutiao/bytedance_log-l2.lua
+/CCS/nginx/lua/bytedance_zx_header.lua
+/CCS/nginx/lua/toutiao/bytedance_log-l2.lua
+/CCS/nginx/lua/toutiao/bytedance_zx_scyd_header.lua
+/CCS/nginx/lua/bytedance_zx_header.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/toutiao/bytedance_log-l2.lua
+/etc/nginx/lua/bytedance_zx_header.lua
+/etc/nginx/lua/toutiao/bytedance_log-l2.lua
+/etc/nginx/lua/toutiao/bytedance_zx_scyd_header.lua
+/etc/nginx/lua/bytedance_zx_header.lua
 </t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>sso.zbom.com</t>
-  </si>
-  <si>
-    <t>/SNS/nginx/ssl/zbom.com.crt
-/SNS/nginx/ssl/zbom.com.key
-/SNS/nginx/sso.zbom.com.conf
-</t>
-  </si>
-  <si>
-    <t>/etc/nginx/ssl/zbom.com.crt
-/etc/nginx/ssl/zbom.com.key
-/etc/nginx/sites-enabled/sso.zbom.com.conf
+    <t>yunchen</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/lua/gdyunchen/yunchen_header.lua
+/SNS/nginx/lua/gdyunchen/yunchen_log.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/gdyunchen/yunchen_header.lua
+/etc/nginx/lua/gdyunchen/yunchen_log.lua
+</t>
+  </si>
+  <si>
+    <t>/CCS/nginx/lua/gdyunchen/yunchen_log-l2.lua
+/CCS/nginx/lua/gdyunchen/yunchen_header-l2.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/gdyunchen/yunchen_log-l2.lua
+/etc/nginx/lua/gdyunchen/yunchen_header-l2.lua
+</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>iqiyi</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/lua/originiqiyi/origin_iqiyi_header_filter.lua
+/SNS/nginx/lua/originiqiyi/origin_iqiyi_log.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/originiqiyi/origin_iqiyi_header_filter.lua
+/etc/nginx/lua/originiqiyi/origin_iqiyi_log.lua
+</t>
+  </si>
+  <si>
+    <t>/CCS/nginx/lua/originiqiyi/origin_iqiyi_header_filter_l2.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/originiqiyi/origin_iqiyi_header_filter_l2.lua
+</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/lua/cdntest.homecloud.komect.com.lua
+/SNS/nginx/lua/tsvp2_migu_logmerge.lua
+/SNS/nginx/lua/gaokao.jilinxiangyun_log.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/cdntest.homecloud.komect.com.lua
+/etc/nginx/lua/tsvp2_migu_logmerge.lua
+/etc/nginx/lua/gaokao.jilinxiangyun_log.lua
+</t>
+  </si>
+  <si>
+    <t>/CCS/nginx/lua/cdntest.homecloud.komect.com.lua
+/CCS/nginx/lua/tsvp2_migu_logmerge-l2.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/cdntest.homecloud.komect.com.lua
+/etc/nginx/lua/tsvp2_migu_logmerge-l2.lua
+</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>common</t>
+  </si>
+  <si>
+    <t>/SNS/nginx/lua/honor/logmerge_honor.lua
+/SNS/nginx/lua/honor/log_honor.lua
+/SNS/nginx/lua/log_wrong_handle.lua
+/SNS/nginx/lua/logmerge.lua
+/SNS/nginx/lua/ngx_common_log.lua
+</t>
+  </si>
+  <si>
+    <t>/etc/nginx/lua/honor/logmerge_honor.lua
+/etc/nginx/lua/honor/log_honor.lua
+/etc/nginx/lua/log_wrong_handle.lua
+/etc/nginx/lua/logmerge.lua
+/etc/nginx/lua/ngx_common_log.lua
 </t>
   </si>
 </sst>
@@ -442,7 +540,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -493,22 +591,97 @@
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
